--- a/reports/ASX_Strong_Buy_Screener_2026-08-05.xlsx
+++ b/reports/ASX_Strong_Buy_Screener_2026-08-05.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report generated: 2026-08-05 00:14 </t>
+          <t xml:space="preserve">Report generated: 2026-08-05 23:41 </t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>6.84</v>
+        <v>6.89</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>9.970000000000001</v>
@@ -926,13 +926,13 @@
         <v>4.88</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.0458</v>
+        <v>0.0435</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.0916</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.1832</v>
+        <v>0.174</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>26.31</v>
+        <v>26.5</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>1.38</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8.35</v>
+        <v>8.23</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>10.63</v>
@@ -1143,24 +1143,24 @@
         <v>7.94</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.0623</v>
+        <v>0.0612</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.1247</v>
+        <v>0.1223</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.2494</v>
+        <v>0.2446</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="5" t="n">
-        <v>10.33</v>
+        <v>10.18</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0.39</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7.39</v>
+        <v>7.47</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7.75</v>
@@ -1210,13 +1210,13 @@
         <v>6.54</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.0036</v>
+        <v>0.0008</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.0072</v>
+        <v>0.0015</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.0144</v>
+        <v>0.003</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>36.95</v>
+        <v>37.35</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>12.75</v>
+        <v>12.89</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.25</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>38.76</v>
+        <v>38.39</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>40.74</v>
@@ -1277,13 +1277,13 @@
         <v>26.78</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0141</v>
+        <v>0.0166</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.0282</v>
+        <v>0.0333</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.0564</v>
+        <v>0.0665</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>114</v>
+        <v>109.69</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>0.29</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>65.23</v>
+        <v>66.22</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>73.29000000000001</v>
@@ -1344,13 +1344,13 @@
         <v>44.18</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.0036</v>
+        <v>-0.0002</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.0072</v>
+        <v>-0.0004</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.0143</v>
+        <v>-0.0008</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>27.52</v>
+        <v>27.82</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>6.37</v>
+        <v>6.47</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>6.22</v>
+        <v>6.31</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>0.31</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1402,22 +1402,22 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>22.21</v>
+        <v>23.02</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>26.17</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>17.99</v>
+        <v>18.025</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.026</v>
+        <v>0.0163</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.0521</v>
+        <v>0.0326</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.1041</v>
+        <v>0.0653</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>35.25</v>
+        <v>36.54</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>6.63</v>
+        <v>6.87</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0.92</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5.54</v>
@@ -1553,13 +1553,13 @@
         <v>4.2</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.0077</v>
+        <v>-0.0048</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.0154</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.0308</v>
+        <v>-0.0192</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>28.06</v>
+        <v>27.72</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>45.88</v>
+        <v>45.33</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>0.3</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>65.34</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>76.40000000000001</v>
@@ -1620,13 +1620,13 @@
         <v>51.2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.0213</v>
+        <v>0.0148</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.0426</v>
+        <v>0.0297</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.0851</v>
+        <v>0.0594</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>36.92</v>
+        <v>37.54</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>1.44</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2.23</v>
@@ -1687,13 +1687,13 @@
         <v>1.14</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.0069</v>
+        <v>-0.0092</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.0139</v>
+        <v>-0.0183</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.0278</v>
+        <v>-0.0367</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>43.2</v>
+        <v>43.6</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>33.86</v>
+        <v>34.67</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>37.54</v>
@@ -1756,13 +1756,13 @@
         <v>25.05</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.0007</v>
+        <v>-0.005</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.0014</v>
+        <v>-0.0101</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0028</v>
+        <v>-0.0202</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>25.65</v>
+        <v>26.07</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.42</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1814,22 +1814,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>38.17</v>
+        <v>38.01</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>41</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>30.56</v>
+        <v>30.7</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.0163</v>
+        <v>-0.0153</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.0326</v>
+        <v>-0.0307</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0613</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>19.38</v>
+        <v>19.29</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>10.3</v>
+        <v>10.18</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>11.1</v>
@@ -1894,13 +1894,13 @@
         <v>8.41</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>-0.0229</v>
+        <v>-0.0183</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>-0.0458</v>
+        <v>-0.0367</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.0916</v>
+        <v>-0.0733</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>85.83</v>
+        <v>84.83</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.89</v>
+        <v>4.83</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>4.77</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>23.85</v>
+        <v>24.04</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>35.64</v>
@@ -1961,13 +1961,13 @@
         <v>19.47</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.0176</v>
+        <v>0.0155</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.0352</v>
+        <v>0.031</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.0704</v>
+        <v>0.062</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>27.41</v>
+        <v>27.63</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>0.52</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>20.35</v>
+        <v>20.22</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>41.34</v>
@@ -2103,13 +2103,13 @@
         <v>16.93</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.034</v>
+        <v>0.0358</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.068</v>
+        <v>0.0716</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.136</v>
+        <v>0.1433</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>19.02</v>
+        <v>18.9</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>5.82</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2228,22 +2228,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>56</v>
+        <v>56.62</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>71.29000000000001</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>44.3</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0007</v>
+        <v>-0.002</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.0014</v>
+        <v>-0.004</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.0029</v>
+        <v>-0.0081</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>20.82</v>
+        <v>21.05</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>9.289999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.12</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>28.76</v>
+        <v>29.16</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>40.28</v>
@@ -2304,13 +2304,13 @@
         <v>22.08</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0499</v>
+        <v>0.0458</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.0998</v>
+        <v>0.0916</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.1997</v>
+        <v>0.1832</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>17.86</v>
+        <v>18.11</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="M22" s="9" t="n">
         <v>0.65</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>4.42</v>
@@ -2446,13 +2446,13 @@
         <v>3.12</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>-0.0199</v>
+        <v>-0.0215</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>-0.0397</v>
+        <v>-0.043</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-0.0795</v>
+        <v>-0.0859</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>23.5</v>
+        <v>23.67</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="M24" s="5" t="n">
         <v>1.37</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>4.14</v>
@@ -2513,13 +2513,13 @@
         <v>0.355</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.0919</v>
+        <v>0.0804</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.1839</v>
+        <v>0.1608</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.3677</v>
+        <v>0.3216</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>13.13</v>
+        <v>13.59</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0.21</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.51</v>
+        <v>11.47</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>13.73</v>
@@ -2580,13 +2580,13 @@
         <v>9.81</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>-0.0195</v>
+        <v>-0.0187</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>-0.0391</v>
+        <v>-0.0375</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>13.53</v>
+        <v>13.48</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0.98</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>6.72</v>
@@ -2649,13 +2649,13 @@
         <v>4.93</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.0188</v>
+        <v>0.0219</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.0375</v>
+        <v>0.0438</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.0751</v>
+        <v>0.0876</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>202.67</v>
+        <v>200.33</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>0.51</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Q27" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>60.52</v>
+        <v>62.54</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>65.98</v>
@@ -2716,13 +2716,13 @@
         <v>39.3</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>-0.0022</v>
+        <v>-0.0106</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>-0.0044</v>
+        <v>-0.0213</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>-0.0089</v>
+        <v>-0.0426</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>21.16</v>
+        <v>21.72</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>5.7</v>
+        <v>5.89</v>
       </c>
       <c r="M28" s="5" t="n">
         <v>0.53</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>6.73</v>
+        <v>6.66</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>8.07</v>
@@ -3008,13 +3008,13 @@
         <v>5.91</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>-0.0171</v>
+        <v>-0.0146</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>-0.0342</v>
+        <v>-0.0293</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>-0.0684</v>
+        <v>-0.0586</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>44.87</v>
+        <v>44.4</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:14</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0.915</v>
+        <v>0.89</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>1.335</v>
@@ -3077,13 +3077,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0382</v>
+        <v>0.0463</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.0765</v>
+        <v>0.0926</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.1529</v>
+        <v>0.1853</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J33" s="5" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>33.82</v>
+        <v>34.23</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>37.11</v>
@@ -3146,13 +3146,13 @@
         <v>25.41</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.0176</v>
+        <v>0.0144</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.0353</v>
+        <v>0.0289</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.0706</v>
+        <v>0.0577</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -3160,13 +3160,13 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>36.37</v>
+        <v>36.81</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>0.28</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3204,22 +3204,22 @@
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>33.79</v>
+        <v>34.77</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>34.3</v>
+        <v>35.1</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>20.23</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.0066</v>
+        <v>-0.0003</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.0133</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.0265</v>
+        <v>-0.0013</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>59.28</v>
+        <v>61</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>4.12</v>
@@ -3282,27 +3282,27 @@
         <v>3.51</v>
       </c>
       <c r="F36" s="7" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="G36" s="7" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="H36" s="7" t="n">
         <v>0.0026</v>
       </c>
-      <c r="H36" s="7" t="n">
-        <v>0.0052</v>
-      </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>10.49</v>
+        <v>10.51</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.93</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>14.77</v>
+        <v>14.81</v>
       </c>
       <c r="M36" s="5" t="n">
         <v>0.32</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>20.01</v>
+        <v>20.37</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>26.93</v>
@@ -3349,13 +3349,13 @@
         <v>16.18</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0176</v>
+        <v>0.0124</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.0352</v>
+        <v>0.0249</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.0704</v>
+        <v>0.0498</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>21.06</v>
+        <v>21.44</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>5.61</v>
+        <v>5.67</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0.85</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>26.9</v>
+        <v>27.08</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>42.06</v>
@@ -3416,13 +3416,13 @@
         <v>21.47</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.0556</v>
+        <v>0.0536</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.1113</v>
+        <v>0.1072</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.2226</v>
+        <v>0.2144</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>34.49</v>
+        <v>34.72</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>8.279999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="M38" s="9" t="n">
         <v>0.51</v>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>180.72</v>
+        <v>178.23</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>185.59</v>
@@ -3483,13 +3483,13 @@
         <v>146.98</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.0794</v>
+        <v>-0.0769</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.1588</v>
+        <v>-0.1539</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.3176</v>
+        <v>-0.3077</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="J39" s="5" t="n">
-        <v>29.05</v>
+        <v>28.65</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>10.62</v>
+        <v>10.47</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>12.79</v>
+        <v>13.37</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>18.48</v>
+        <v>18.065</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>9.5</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.0987</v>
+        <v>0.0761</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.1974</v>
+        <v>0.1522</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.3948</v>
+        <v>0.3044</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>9.34</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>0.54</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>9.94</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>10.85</v>
@@ -3694,13 +3694,13 @@
         <v>7.25</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0125</v>
+        <v>0.0143</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.025</v>
+        <v>0.0287</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>0.0499</v>
+        <v>0.0574</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
@@ -3708,13 +3708,13 @@
         </is>
       </c>
       <c r="J42" s="5" t="n">
-        <v>16.03</v>
+        <v>15.92</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>1.96</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>23.78</v>
+        <v>24.02</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>25.95</v>
@@ -3761,13 +3761,13 @@
         <v>18.18</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0074</v>
+        <v>0.0048</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.0148</v>
+        <v>0.0097</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.0296</v>
+        <v>0.0193</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
@@ -3775,13 +3775,13 @@
         </is>
       </c>
       <c r="J43" s="5" t="n">
-        <v>21.23</v>
+        <v>21.45</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>13.06</v>
+        <v>13.2</v>
       </c>
       <c r="M43" s="5" t="n">
         <v>0.18</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>6.685</v>
@@ -3828,13 +3828,13 @@
         <v>3.215</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.1126</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0.2251</v>
+        <v>0.1972</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.4503</v>
+        <v>0.3944</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>17.05</v>
+        <v>17</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>1.17</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3932,12 +3932,12 @@
       </c>
       <c r="P45" s="8" t="inlineStr">
         <is>
-          <t>Centuria Industrial REIT is Australia's largest domestic pure play industrial REIT and is included in the S&amp;P/ASX 200 Index. CIP's portfolio of high-quality industrial assets is situated in urban infill locations throughout Australia and is underpinned by a quality and diverse tenant base. CIP is overseen by a hands-on, active manager and provides investors with income and an opportunity for ca...</t>
+          <t>Centuria Industrial REIT is Australia's largest domestic pure play industrial REIT and is included in the S&amp;P/ASX 200 Index. CIP's portfolio of high-quality industrial assets is situated in key metropolitan locations throughout Au stralia and is underpinned by a quality and diverse tenant base. CIP is overseen by a hand on, active manager and provides investors with income and an opportunity fo...</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>8.380000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>12.73</v>
@@ -3962,13 +3962,13 @@
         <v>7.64</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.0563</v>
+        <v>0.0634</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>0.1127</v>
+        <v>0.1269</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.2254</v>
+        <v>0.2538</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -3976,13 +3976,13 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>21.49</v>
+        <v>21</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="M46" s="9" t="n">
         <v>2</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Q46" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>4.66</v>
@@ -4029,13 +4029,13 @@
         <v>3.3</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.0073</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.0145</v>
+        <v>0.0186</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0.029</v>
+        <v>0.0371</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="J47" s="5" t="n">
-        <v>12.42</v>
+        <v>12.32</v>
       </c>
       <c r="K47" s="5" t="n">
         <v>0.82</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>7.81</v>
+        <v>7.75</v>
       </c>
       <c r="M47" s="5" t="n">
         <v>0.57</v>
@@ -4071,74 +4071,74 @@
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>CMW</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Cromwell Property Group</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="10" t="n">
         <v>0.435</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="11" t="n">
         <v>0.06610000000000001</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="11" t="n">
         <v>0.1322</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H48" s="11" t="n">
         <v>0.2644</v>
       </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="n">
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
         <v>10.88</v>
       </c>
-      <c r="K48" s="5" t="n">
+      <c r="K48" s="9" t="n">
         <v>0.75</v>
       </c>
-      <c r="L48" s="5" t="n">
+      <c r="L48" s="9" t="n">
         <v>4.57</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="M48" s="9" t="n">
         <v>0.49</v>
       </c>
-      <c r="N48" s="8" t="inlineStr">
+      <c r="N48" s="12" t="inlineStr">
         <is>
           <t>2025: $176.6M | 2024: $187.7M | 2023: $349.4M | 2022: $352.5M</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="12" t="inlineStr">
         <is>
           <t>2025: $-22.6M | 2024: $-541.1M | 2023: $-443.8M | 2022: $263.2M</t>
         </is>
       </c>
-      <c r="P48" s="8" t="inlineStr">
+      <c r="P48" s="12" t="inlineStr">
         <is>
           <t>Cromwell Property Group is a real estate investor and manager with $5.0 billion of assets under management in Australia and New Zealand on 31 December 2025. Cromwell is a trusted partner to a broad range of local and global investors, capital providers and banking partners, with a strong track record of creating value and delivering risk-adjusted returns throughout the real estate investment cy...</t>
         </is>
       </c>
-      <c r="Q48" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05 00:15</t>
+      <c r="Q48" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>7.97</v>
+        <v>7.9</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>8.960000000000001</v>
@@ -4163,13 +4163,13 @@
         <v>7.44</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0146</v>
+        <v>0.0168</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.0292</v>
+        <v>0.0337</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.0585</v>
+        <v>0.0673</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="J49" s="5" t="n">
-        <v>159.4</v>
+        <v>158</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>11.07</v>
+        <v>10.96</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>9.800000000000001</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>122.32</v>
+        <v>122</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>315.22</v>
@@ -4230,13 +4230,13 @@
         <v>88.73999999999999</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0059</v>
+        <v>0.0065</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.0117</v>
+        <v>0.0131</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>0.0235</v>
+        <v>0.0261</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
@@ -4244,13 +4244,13 @@
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>23.21</v>
+        <v>23.15</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="M50" s="5" t="n">
         <v>0.12</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>24.33</v>
+        <v>24.22</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>24.59</v>
@@ -4297,13 +4297,13 @@
         <v>20.1</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.0058</v>
+        <v>-0.0047</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.0116</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.0231</v>
+        <v>-0.0187</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="J51" s="5" t="n">
-        <v>32.01</v>
+        <v>31.87</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>0.72</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4355,22 +4355,22 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>42.64</v>
+        <v>43.26</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>42.64</v>
+        <v>43.39</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>26.73</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>-0.0297</v>
+        <v>-0.0332</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>-0.0593</v>
+        <v>-0.0663</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>-0.1186</v>
+        <v>-0.1326</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>29.21</v>
+        <v>29.63</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>7.74</v>
+        <v>7.8</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="Q53" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>128.83</v>
+        <v>130.66</v>
       </c>
       <c r="D54" s="6" t="n">
         <v>273.45</v>
@@ -4500,13 +4500,13 @@
         <v>90</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0164</v>
+        <v>0.0122</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0.0329</v>
+        <v>0.0245</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="J54" s="5" t="n">
-        <v>14.71</v>
+        <v>14.81</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>9.07</v>
+        <v>9.33</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>14</v>
@@ -4636,13 +4636,13 @@
         <v>8.35</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>0.3851</v>
+        <v>0.3674</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>0.7702</v>
+        <v>0.7348</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>1.5404</v>
+        <v>1.4696</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -4650,13 +4650,13 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>14.17</v>
+        <v>14.58</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="M56" s="9" t="n">
         <v>0.13</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="D57" s="10" t="n">
         <v>2.96</v>
@@ -4703,13 +4703,13 @@
         <v>2.14</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0.0636</v>
+        <v>0.0622</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>0.1271</v>
+        <v>0.1245</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>0.2543</v>
+        <v>0.249</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M57" s="9" t="n">
         <v>0.8</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="Q57" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:41</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>19.92</v>
+        <v>19.29</v>
       </c>
       <c r="D59" s="6" t="n">
         <v>24.58</v>
@@ -4845,13 +4845,13 @@
         <v>13.11</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.001</v>
+        <v>0.0071</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.002</v>
+        <v>0.0143</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-0.004</v>
+        <v>0.0285</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="J59" s="5" t="n">
-        <v>31.12</v>
+        <v>30.14</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="M59" s="5" t="n">
         <v>1.81</v>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>7.95</v>
+        <v>7.98</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>8.654999999999999</v>
@@ -4912,13 +4912,13 @@
         <v>6.8</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.0116</v>
+        <v>0.0107</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.0233</v>
+        <v>0.0213</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>0.0465</v>
+        <v>0.0426</v>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="J60" s="5" t="n">
-        <v>33.12</v>
+        <v>33.25</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0.52</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>4.78</v>
@@ -4979,13 +4979,13 @@
         <v>3.67</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.0224</v>
+        <v>0.023</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.0447</v>
+        <v>0.046</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="J61" s="5" t="n">
-        <v>12.68</v>
+        <v>12.65</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>16.45</v>
+        <v>16.41</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M61" s="5" t="n">
         <v>1.13</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>7.73</v>
@@ -5046,13 +5046,13 @@
         <v>5.3</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0.029</v>
+        <v>0.0294</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>0.058</v>
+        <v>0.0589</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>0.1159</v>
+        <v>0.1178</v>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>13.2</v>
+        <v>13.17</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>0.68</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="M62" s="5" t="n">
         <v>0.47</v>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="D63" s="10" t="n">
         <v>7.91</v>
@@ -5113,13 +5113,13 @@
         <v>4.96</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0.042</v>
+        <v>0.0431</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0861</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>0.168</v>
+        <v>0.1722</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>22.32</v>
+        <v>22.24</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0.96</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="Q63" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>0.32</v>
+        <v>0.325</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>1.145</v>
@@ -5180,13 +5180,13 @@
         <v>0.285</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0.5137</v>
+        <v>0.5019</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>1.0273</v>
+        <v>1.0038</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>2.0547</v>
+        <v>2.0077</v>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
@@ -5194,13 +5194,13 @@
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>7.35</v>
+        <v>7.47</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="M64" s="5" t="n">
         <v>0.57</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5238,22 +5238,22 @@
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>11.78</v>
+        <v>12.52</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>17.75</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>7.14</v>
+        <v>7.42</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.0194</v>
+        <v>0.0035</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0.0388</v>
+        <v>0.007</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.0776</v>
+        <v>0.0139</v>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="J65" s="5" t="n">
-        <v>17.85</v>
+        <v>18.97</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>4.25</v>
+        <v>4.51</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="D66" s="6" t="n">
         <v>3.44</v>
@@ -5316,13 +5316,13 @@
         <v>2.22</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>-0.012</v>
+        <v>-0.0165</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>-0.024</v>
+        <v>-0.0331</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>-0.048</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
@@ -5330,13 +5330,13 @@
         </is>
       </c>
       <c r="J66" s="5" t="n">
-        <v>20.28</v>
+        <v>20.68</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M66" s="5" t="n">
         <v>0.6899999999999999</v>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>13.18</v>
+        <v>13.58</v>
       </c>
       <c r="D67" s="10" t="n">
         <v>16.56</v>
@@ -5383,13 +5383,13 @@
         <v>9.609999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0198</v>
       </c>
       <c r="G67" s="11" t="n">
-        <v>0.056</v>
+        <v>0.0396</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>0.1119</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>26.36</v>
+        <v>27.16</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="M67" s="9" t="n">
         <v>1.09</v>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="Q67" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5441,22 +5441,22 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>18.08</v>
+        <v>18.19</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>23.38</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>17.65</v>
+        <v>17.7</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>-0.0038</v>
+        <v>-0.0056</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>-0.0075</v>
+        <v>-0.0112</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>-0.015</v>
+        <v>-0.0224</v>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
@@ -5464,13 +5464,13 @@
         </is>
       </c>
       <c r="J68" s="5" t="n">
-        <v>10.45</v>
+        <v>10.58</v>
       </c>
       <c r="K68" s="5" t="n">
         <v>1.89</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="M68" s="5" t="n">
         <v>0.28</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5508,22 +5508,22 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>35.13</v>
+        <v>35.57</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>35.31</v>
+        <v>35.9</v>
       </c>
       <c r="E69" s="10" t="n">
         <v>26.51</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>0.0121</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G69" s="11" t="n">
-        <v>0.0242</v>
+        <v>0.0175</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>0.0484</v>
+        <v>0.035</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
@@ -5531,13 +5531,13 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>53.23</v>
+        <v>53.09</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>11.65</v>
+        <v>11.78</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>8.94</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M69" s="9" t="n">
         <v>6.91</v>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Q69" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>30.2</v>
+        <v>30.77</v>
       </c>
       <c r="D70" s="10" t="n">
         <v>37.31</v>
@@ -5584,13 +5584,13 @@
         <v>24.56</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>0.0385</v>
+        <v>0.0331</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>0.0769</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>0.1539</v>
+        <v>0.1325</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>35.95</v>
+        <v>36.63</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>5.53</v>
+        <v>5.41</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>9.130000000000001</v>
@@ -5653,13 +5653,13 @@
         <v>4.69</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>0.0335</v>
+        <v>0.0398</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0.0669</v>
+        <v>0.0795</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0.1339</v>
+        <v>0.159</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="J71" s="5" t="n">
-        <v>24.99</v>
+        <v>24.45</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="L71" s="5" t="n">
         <v>0.17</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="Q73" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>5.22</v>
+        <v>5.24</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>5.75</v>
@@ -5862,13 +5862,13 @@
         <v>4.42</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>0.0141</v>
+        <v>0.013</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>0.0281</v>
+        <v>0.0261</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>0.0562</v>
+        <v>0.0522</v>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>10.24</v>
+        <v>10.27</v>
       </c>
       <c r="K74" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>9.630000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="M74" s="5" t="n">
         <v>0.53</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>86.25</v>
+        <v>89.03</v>
       </c>
       <c r="D77" s="10" t="n">
         <v>122.03</v>
@@ -6071,13 +6071,13 @@
         <v>68.7</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>0.0368</v>
+        <v>0.0279</v>
       </c>
       <c r="G77" s="11" t="n">
-        <v>0.0737</v>
+        <v>0.0558</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>0.1473</v>
+        <v>0.1115</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>66.86</v>
+        <v>69.55</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>12.91</v>
+        <v>13.33</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>15.56</v>
+        <v>16.06</v>
       </c>
       <c r="M77" s="9" t="n">
         <v>0.11</v>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="Q77" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>4.96</v>
+        <v>4.97</v>
       </c>
       <c r="D78" s="6" t="n">
         <v>7.7</v>
@@ -6138,13 +6138,13 @@
         <v>4.28</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>0.011</v>
+        <v>0.0105</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0.0221</v>
+        <v>0.021</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>0.0442</v>
+        <v>0.0421</v>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>11.02</v>
+        <v>11.04</v>
       </c>
       <c r="K78" s="5" t="n">
         <v>1.26</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Q78" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>8.56</v>
+        <v>8.58</v>
       </c>
       <c r="D79" s="6" t="n">
         <v>9.17</v>
@@ -6205,13 +6205,13 @@
         <v>6.39</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.0019</v>
+        <v>-0.0025</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.0038</v>
+        <v>-0.005</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.0076</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>18.61</v>
+        <v>18.65</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>6.735</v>
@@ -6274,13 +6274,13 @@
         <v>1.995</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>0.1959</v>
+        <v>0.1866</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>0.3918</v>
+        <v>0.3733</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>0.7837</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
@@ -6288,13 +6288,13 @@
         </is>
       </c>
       <c r="J80" s="5" t="n">
-        <v>78.33</v>
+        <v>80</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="M80" s="5" t="n">
         <v>0.9</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Q80" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>10.05</v>
@@ -6416,13 +6416,13 @@
         <v>4.1</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>0.0238</v>
+        <v>0.0203</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.0475</v>
+        <v>0.0407</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>0.095</v>
+        <v>0.0813</v>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="J82" s="5" t="n">
-        <v>11.11</v>
+        <v>11.25</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>12.3</v>
+        <v>12.45</v>
       </c>
       <c r="M82" s="5" t="n">
         <v>1.02</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Q82" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>6.53</v>
+        <v>6.71</v>
       </c>
       <c r="D83" s="10" t="n">
         <v>9.48</v>
@@ -6483,13 +6483,13 @@
         <v>4.92</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>0.0536</v>
+        <v>0.0455</v>
       </c>
       <c r="G83" s="11" t="n">
-        <v>0.1072</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>0.2144</v>
+        <v>0.1818</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -6497,13 +6497,13 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>-22.81</v>
+        <v>-23.44</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="M83" s="9" t="n">
         <v>0.55</v>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="Q83" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>4.44</v>
+        <v>4.48</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>6.24</v>
@@ -6550,13 +6550,13 @@
         <v>3.64</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>0.0349</v>
+        <v>0.0324</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>0.0698</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H84" s="11" t="n">
-        <v>0.1396</v>
+        <v>0.1295</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>13.06</v>
+        <v>13.18</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="M84" s="9" t="n">
         <v>0.58</v>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="Q84" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="D85" s="6" t="n">
         <v>3.56</v>
@@ -6617,13 +6617,13 @@
         <v>1.69</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.0256</v>
+        <v>0.0348</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0.0512</v>
+        <v>0.0696</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.1024</v>
+        <v>0.1392</v>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>14.47</v>
+        <v>14</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="M85" s="5" t="n">
         <v>5.85</v>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>5.655</v>
@@ -6684,13 +6684,13 @@
         <v>3.155</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>0.0224</v>
+        <v>0.0205</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0.0448</v>
+        <v>0.0411</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>0.0897</v>
+        <v>0.0822</v>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
@@ -6698,13 +6698,13 @@
         </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>15.46</v>
+        <v>15.57</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M86" s="5" t="n">
         <v>0.65</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Q86" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>7.06</v>
+        <v>7.25</v>
       </c>
       <c r="D88" s="10" t="n">
         <v>10.38</v>
@@ -6826,13 +6826,13 @@
         <v>5.64</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0791</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>0.1759</v>
+        <v>0.1582</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>0.3518</v>
+        <v>0.3164</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -6840,13 +6840,13 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>17.22</v>
+        <v>17.68</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="M88" s="9" t="n">
         <v>0.39</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="Q88" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>82.84</v>
+        <v>82.22</v>
       </c>
       <c r="D90" s="6" t="n">
         <v>121</v>
@@ -6968,13 +6968,13 @@
         <v>67.38</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>-0.0104</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>-0.0207</v>
+        <v>-0.0171</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>-0.0414</v>
+        <v>-0.0342</v>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="J90" s="5" t="n">
-        <v>18.83</v>
+        <v>18.69</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="M90" s="5" t="n">
         <v>0.43</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Q90" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>39.21</v>
+        <v>40.21</v>
       </c>
       <c r="D92" s="10" t="n">
         <v>45.98</v>
@@ -7110,13 +7110,13 @@
         <v>24.41</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>-0.0076</v>
+        <v>-0.014</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>-0.0152</v>
+        <v>-0.028</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>-0.0305</v>
+        <v>-0.056</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>145.22</v>
+        <v>148.93</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>4.71</v>
+        <v>4.83</v>
       </c>
       <c r="M92" s="9" t="n">
         <v>0.74</v>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="D93" s="10" t="n">
         <v>5.22</v>
@@ -7177,13 +7177,13 @@
         <v>3.68</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.035</v>
+        <v>0.0356</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>0.14</v>
+        <v>0.1425</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>18.88</v>
+        <v>18.83</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>1.29</v>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="Q93" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>5.95</v>
@@ -7244,13 +7244,13 @@
         <v>2.4</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>0.1565</v>
+        <v>0.148</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>0.313</v>
+        <v>0.2959</v>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>7.91</v>
+        <v>8.01</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="L94" s="5" t="n">
         <v>0.35</v>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="Q94" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7377,22 +7377,22 @@
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>14.96</v>
+        <v>15.59</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>22.37</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>11.65</v>
+        <v>11.9</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>0.0555</v>
+        <v>0.0432</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0.111</v>
+        <v>0.0863</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>0.2221</v>
+        <v>0.1727</v>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
@@ -7400,13 +7400,13 @@
         </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>187</v>
+        <v>194.88</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>4.48</v>
+        <v>4.66</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>21.03</v>
+        <v>21.92</v>
       </c>
       <c r="M96" s="5" t="n">
         <v>6.32</v>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="Q96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>10.07</v>
+        <v>10.36</v>
       </c>
       <c r="D97" s="6" t="n">
         <v>11.8</v>
@@ -7453,13 +7453,13 @@
         <v>7.96</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-0.0157</v>
+        <v>-0.0223</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>-0.0314</v>
+        <v>-0.0445</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
@@ -7467,13 +7467,13 @@
         </is>
       </c>
       <c r="J97" s="5" t="n">
-        <v>12.43</v>
+        <v>12.79</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>11.22</v>
+        <v>11.54</v>
       </c>
       <c r="M97" s="5" t="n">
         <v>0.38</v>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="D98" s="10" t="n">
         <v>2.46</v>
@@ -7520,13 +7520,13 @@
         <v>1.607</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>0.0342</v>
+        <v>0.0326</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>0.0683</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.1366</v>
+        <v>0.1304</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -7534,13 +7534,13 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0.78</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M98" s="9" t="n">
         <v>0.44</v>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="Q98" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7578,22 +7578,22 @@
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>59.37</v>
+        <v>60.73</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>74.94</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>31.38</v>
+        <v>32.515</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.0356</v>
+        <v>0.0293</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0.0713</v>
+        <v>0.0585</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.1426</v>
+        <v>0.117</v>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         </is>
       </c>
       <c r="J99" s="5" t="n">
-        <v>29.39</v>
+        <v>30.06</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M99" s="5" t="n">
         <v>1.31</v>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>263.19</v>
+        <v>267.09</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>263.19</v>
+        <v>267.72</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>187.31</v>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>42.85</v>
+        <v>42.53</v>
       </c>
       <c r="D103" s="6" t="n">
         <v>49.45</v>
@@ -7865,13 +7865,13 @@
         <v>35.48</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.0262</v>
+        <v>-0.0245</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.0524</v>
+        <v>-0.049</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.1048</v>
+        <v>-0.098</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="J103" s="5" t="n">
-        <v>21.43</v>
+        <v>21.27</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
@@ -7911,74 +7911,74 @@
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>Nanosonics Limited</t>
         </is>
       </c>
-      <c r="C104" s="10" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="D104" s="10" t="n">
+      <c r="C104" s="6" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="D104" s="6" t="n">
         <v>4.77</v>
       </c>
-      <c r="E104" s="10" t="n">
+      <c r="E104" s="6" t="n">
         <v>2.94</v>
       </c>
-      <c r="F104" s="11" t="n">
-        <v>0.0664</v>
-      </c>
-      <c r="G104" s="11" t="n">
-        <v>0.1328</v>
-      </c>
-      <c r="H104" s="11" t="n">
-        <v>0.2656</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J104" s="9" t="n">
-        <v>48.14</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="L104" s="9" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="M104" s="9" t="n">
+      <c r="F104" s="7" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M104" s="5" t="n">
         <v>3.04</v>
       </c>
-      <c r="N104" s="12" t="inlineStr">
+      <c r="N104" s="8" t="inlineStr">
         <is>
           <t>2025: $198.9M | 2024: $171.6M | 2023: $167.5M | 2022: $119.7M</t>
         </is>
       </c>
-      <c r="O104" s="12" t="inlineStr">
+      <c r="O104" s="8" t="inlineStr">
         <is>
           <t>2025: $20.7M | 2024: $13.0M | 2023: $19.9M | 2022: $3.7M</t>
         </is>
       </c>
-      <c r="P104" s="12" t="inlineStr">
+      <c r="P104" s="8" t="inlineStr">
         <is>
           <t>Nanosonics Limited operates as an infection prevention company in Australia, North America, Europe, the United Kingdom, the Middle East, and Asia Pacific. The company manufactures and distributes trophon ultrasound probe disinfector, and its related consumables and accessories; and research, develops, and commercialize of infection control and decontamination products and related technologies. ...</t>
         </is>
       </c>
-      <c r="Q104" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-05 00:15</t>
+      <c r="Q104" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>0.98</v>
+        <v>0.995</v>
       </c>
       <c r="D105" s="10" t="n">
         <v>1.9</v>
@@ -8003,13 +8003,13 @@
         <v>0.835</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.0785</v>
+        <v>0.0736</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.157</v>
+        <v>0.1471</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>0.3141</v>
+        <v>0.2943</v>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
@@ -8017,13 +8017,13 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>14</v>
+        <v>14.21</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="M105" s="9" t="n">
         <v>0.17</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="Q105" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>7.52</v>
+        <v>7.47</v>
       </c>
       <c r="D106" s="6" t="n">
         <v>8.26</v>
@@ -8070,13 +8070,13 @@
         <v>5.79</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>0.01</v>
+        <v>0.0117</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.0199</v>
+        <v>0.0234</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>0.0399</v>
+        <v>0.0469</v>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
@@ -8084,13 +8084,13 @@
         </is>
       </c>
       <c r="J106" s="5" t="n">
-        <v>18.8</v>
+        <v>18.68</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="M106" s="5" t="n">
         <v>0.25</v>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8203,22 +8203,22 @@
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>20.32</v>
+        <v>21.49</v>
       </c>
       <c r="D108" s="6" t="n">
         <v>31.96</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>16.27</v>
+        <v>16.55</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>0.0442</v>
+        <v>0.0282</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>0.0885</v>
+        <v>0.0564</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>0.1769</v>
+        <v>0.1129</v>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="J108" s="5" t="n">
-        <v>17.37</v>
+        <v>18.37</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>4.16</v>
+        <v>4.4</v>
       </c>
       <c r="M108" s="5" t="n">
         <v>0.12</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="Q108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8270,22 +8270,22 @@
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>1.79</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>0.0339</v>
+        <v>0.0358</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0.0678</v>
+        <v>0.0716</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>0.1356</v>
+        <v>0.1431</v>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="J109" s="5" t="n">
-        <v>15.67</v>
+        <v>15.57</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>23.24</v>
+        <v>24.38</v>
       </c>
       <c r="D110" s="6" t="n">
         <v>38.3</v>
@@ -8348,13 +8348,13 @@
         <v>19.805</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>0.0427</v>
+        <v>0.0292</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.0854</v>
+        <v>0.0584</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>0.1708</v>
+        <v>0.1169</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="J110" s="5" t="n">
-        <v>101.04</v>
+        <v>106</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>38.1</v>
+        <v>39.97</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>15.78</v>
+        <v>16.56</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>8.369999999999999</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Q110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>45.5</v>
+        <v>46.92</v>
       </c>
       <c r="D111" s="10" t="n">
         <v>57.16</v>
@@ -8415,13 +8415,13 @@
         <v>36.01</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>0.0409</v>
+        <v>0.0317</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>0.0818</v>
+        <v>0.0634</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>0.1635</v>
+        <v>0.1267</v>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
@@ -8429,13 +8429,13 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>40.27</v>
+        <v>41.52</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="M111" s="9" t="n">
         <v>0.32</v>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="Q111" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>14.04</v>
+        <v>14.21</v>
       </c>
       <c r="D112" s="10" t="n">
         <v>18.22</v>
@@ -8482,13 +8482,13 @@
         <v>10.91</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>0.1083</v>
+        <v>0.104</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>0.2165</v>
+        <v>0.208</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>0.4331</v>
+        <v>0.416</v>
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>-34.76</v>
+        <v>-35.18</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>23.54</v>
+        <v>23.83</v>
       </c>
       <c r="M112" s="9" t="n">
         <v>0.6</v>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>1.525</v>
+        <v>1.52</v>
       </c>
       <c r="D113" s="6" t="n">
         <v>2.43</v>
@@ -8549,13 +8549,13 @@
         <v>1.212</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.0358</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0.0698</v>
+        <v>0.0716</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.1395</v>
+        <v>0.1433</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="J113" s="5" t="n">
-        <v>15.25</v>
+        <v>15.2</v>
       </c>
       <c r="K113" s="5" t="n">
         <v>0.68</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>11.01</v>
+        <v>10.79</v>
       </c>
       <c r="D114" s="6" t="n">
         <v>13.13</v>
@@ -8616,13 +8616,13 @@
         <v>10.02</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>0.0169</v>
+        <v>0.0224</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>0.0339</v>
+        <v>0.0448</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>0.0678</v>
+        <v>0.0896</v>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
@@ -8630,13 +8630,13 @@
         </is>
       </c>
       <c r="J114" s="5" t="n">
-        <v>18.66</v>
+        <v>18.29</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="M114" s="5" t="n">
         <v>0.48</v>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="Q114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>23.65</v>
+        <v>23.87</v>
       </c>
       <c r="D115" s="10" t="n">
         <v>26.47</v>
@@ -8683,13 +8683,13 @@
         <v>18.58</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>0.0235</v>
+        <v>0.021</v>
       </c>
       <c r="G115" s="11" t="n">
-        <v>0.047</v>
+        <v>0.042</v>
       </c>
       <c r="H115" s="11" t="n">
-        <v>0.094</v>
+        <v>0.0839</v>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>46.37</v>
+        <v>46.8</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L115" s="9" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="Q115" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:15</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="Q116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="C117" s="6" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="D117" s="6" t="n">
         <v>6.81</v>
@@ -8827,13 +8827,13 @@
         <v>1.675</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>0.051</v>
+        <v>0.0475</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>0.102</v>
+        <v>0.095</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>0.204</v>
+        <v>0.1901</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
@@ -8841,13 +8841,13 @@
         </is>
       </c>
       <c r="J117" s="5" t="n">
-        <v>11.36</v>
+        <v>11.5</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>14.26</v>
+        <v>14.43</v>
       </c>
       <c r="M117" s="5" t="n">
         <v>0.2</v>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>172.82</v>
+        <v>180.14</v>
       </c>
       <c r="D118" s="10" t="n">
         <v>324.49</v>
@@ -8894,13 +8894,13 @@
         <v>107.75</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>0.0256</v>
+        <v>0.0144</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>0.0513</v>
+        <v>0.0289</v>
       </c>
       <c r="H118" s="11" t="n">
-        <v>0.1026</v>
+        <v>0.0578</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
@@ -8908,13 +8908,13 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>77.15000000000001</v>
+        <v>80.06</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>46.43</v>
+        <v>48.4</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>75.05</v>
+        <v>78.23</v>
       </c>
       <c r="M118" s="9" t="n">
         <v>0.66</v>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>13.27</v>
+        <v>13.34</v>
       </c>
       <c r="D119" s="10" t="n">
         <v>22.92</v>
@@ -8961,13 +8961,13 @@
         <v>10.97</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>0.0571</v>
+        <v>0.0555</v>
       </c>
       <c r="G119" s="11" t="n">
-        <v>0.1141</v>
+        <v>0.1109</v>
       </c>
       <c r="H119" s="11" t="n">
-        <v>0.2283</v>
+        <v>0.2218</v>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
@@ -8975,13 +8975,13 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>14.74</v>
+        <v>14.82</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="M119" s="9" t="n">
         <v>0.24</v>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="Q119" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>18.58</v>
+        <v>18.7</v>
       </c>
       <c r="D120" s="6" t="n">
         <v>22.32</v>
@@ -9028,13 +9028,13 @@
         <v>15.1</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>0.0323</v>
+        <v>0.0305</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0611</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>0.1294</v>
+        <v>0.1221</v>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
@@ -9042,13 +9042,13 @@
         </is>
       </c>
       <c r="J120" s="5" t="n">
-        <v>11.38</v>
+        <v>11.46</v>
       </c>
       <c r="K120" s="5" t="n">
         <v>1.31</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M120" s="5" t="n">
         <v>0.5600000000000001</v>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="Q120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>10.29</v>
+        <v>10.6</v>
       </c>
       <c r="D121" s="10" t="n">
         <v>12.62</v>
@@ -9095,13 +9095,13 @@
         <v>8.035</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>0.0305</v>
+        <v>0.0223</v>
       </c>
       <c r="G121" s="11" t="n">
-        <v>0.061</v>
+        <v>0.0446</v>
       </c>
       <c r="H121" s="11" t="n">
-        <v>0.122</v>
+        <v>0.0892</v>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>11.59</v>
+        <v>11.94</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="M121" s="9" t="n">
         <v>6.11</v>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="Q121" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>24.93</v>
+        <v>24.61</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>25.83</v>
@@ -9162,13 +9162,13 @@
         <v>18.57</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>-0.0056</v>
+        <v>-0.0025</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>-0.0112</v>
+        <v>-0.0051</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>-0.0224</v>
+        <v>-0.0102</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="J122" s="5" t="n">
-        <v>12.4</v>
+        <v>12.12</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="Q122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>163.56</v>
+        <v>166.32</v>
       </c>
       <c r="D124" s="6" t="n">
         <v>265.98</v>
@@ -9298,13 +9298,13 @@
         <v>131.07</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>0.0395</v>
+        <v>0.0344</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>0.079</v>
+        <v>0.0688</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>0.158</v>
+        <v>0.1376</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="J124" s="5" t="n">
-        <v>37.69</v>
+        <v>38.32</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>10.5</v>
+        <v>10.68</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>10.94</v>
+        <v>11.12</v>
       </c>
       <c r="M124" s="5" t="n">
         <v>4.3</v>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="Q124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="C125" s="6" t="n">
-        <v>43.94</v>
+        <v>43.55</v>
       </c>
       <c r="D125" s="6" t="n">
         <v>45.49</v>
@@ -9365,13 +9365,13 @@
         <v>30.39</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.0008</v>
+        <v>0.0012</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>-0.0015</v>
+        <v>0.0024</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>-0.003</v>
+        <v>0.0048</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="J125" s="5" t="n">
-        <v>34.87</v>
+        <v>34.56</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>0.54</v>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>172.39</v>
+        <v>176.34</v>
       </c>
       <c r="D126" s="6" t="n">
         <v>195.84</v>
@@ -9432,13 +9432,13 @@
         <v>111.55</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>-0.0053</v>
+        <v>-0.0112</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>-0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>-0.0214</v>
+        <v>-0.0447</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
@@ -9446,13 +9446,13 @@
         </is>
       </c>
       <c r="J126" s="5" t="n">
-        <v>16.45</v>
+        <v>16.83</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="M126" s="5" t="n">
         <v>0.32</v>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="Q126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>30.7</v>
+        <v>31.39</v>
       </c>
       <c r="D127" s="10" t="n">
         <v>45.25</v>
@@ -9499,13 +9499,13 @@
         <v>25.5</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>0.0737</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G127" s="11" t="n">
-        <v>0.1475</v>
+        <v>0.1324</v>
       </c>
       <c r="H127" s="11" t="n">
-        <v>0.295</v>
+        <v>0.2647</v>
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
@@ -9513,13 +9513,13 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>20.88</v>
+        <v>21.21</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>8.039999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M127" s="9" t="n">
         <v>0.13</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="Q127" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>6.24</v>
+        <v>6.7</v>
       </c>
       <c r="D128" s="6" t="n">
         <v>10</v>
@@ -9566,13 +9566,13 @@
         <v>4.06</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>0.0492</v>
+        <v>0.0287</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>0.0985</v>
+        <v>0.0574</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>0.197</v>
+        <v>0.1148</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="J128" s="5" t="n">
-        <v>9.75</v>
+        <v>10.47</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>2.49</v>
+        <v>2.67</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="M128" s="5" t="n">
         <v>5.8</v>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="Q128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="D129" s="10" t="n">
         <v>4.62</v>
@@ -9633,13 +9633,13 @@
         <v>2.86</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>0.0431</v>
+        <v>0.0413</v>
       </c>
       <c r="G129" s="11" t="n">
-        <v>0.0862</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H129" s="11" t="n">
-        <v>0.1723</v>
+        <v>0.1651</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>19.47</v>
+        <v>19.58</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>1.45</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="M129" s="9" t="n">
         <v>0.33</v>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="Q129" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
       <c r="D130" s="6" t="n">
         <v>4.95</v>
@@ -9700,13 +9700,13 @@
         <v>2.52</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>0.0008</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>0.0015</v>
+        <v>-0.0192</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>0.003</v>
+        <v>-0.0384</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
@@ -9714,13 +9714,13 @@
         </is>
       </c>
       <c r="J130" s="5" t="n">
-        <v>39</v>
+        <v>40.67</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="M130" s="5" t="n">
         <v>0.18</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="C131" s="6" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="D131" s="6" t="n">
         <v>4.27</v>
@@ -9767,13 +9767,13 @@
         <v>3.275</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>0.0069</v>
+        <v>0.0076</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>0.0139</v>
+        <v>0.0152</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.0278</v>
+        <v>0.0304</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
@@ -9781,13 +9781,13 @@
         </is>
       </c>
       <c r="J131" s="5" t="n">
-        <v>11.74</v>
+        <v>11.71</v>
       </c>
       <c r="K131" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>7.76</v>
+        <v>7.74</v>
       </c>
       <c r="M131" s="5" t="n">
         <v>0.79</v>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="C133" s="6" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="D133" s="6" t="n">
         <v>6.665</v>
@@ -9903,13 +9903,13 @@
         <v>3.87</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>0.0245</v>
+        <v>0.0224</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.049</v>
+        <v>0.0448</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.0979</v>
+        <v>0.0896</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -9917,13 +9917,13 @@
         </is>
       </c>
       <c r="J133" s="5" t="n">
-        <v>16.44</v>
+        <v>16.56</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="M133" s="5" t="n">
         <v>0.76</v>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>15.01</v>
+        <v>15.07</v>
       </c>
       <c r="D134" s="10" t="n">
         <v>29.84</v>
@@ -9970,13 +9970,13 @@
         <v>11.745</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>0.093</v>
+        <v>0.0916</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>0.186</v>
+        <v>0.1832</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>0.3719</v>
+        <v>0.3665</v>
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
@@ -9984,13 +9984,13 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>23.5</v>
+        <v>23.59</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="M134" s="9" t="n">
         <v>0.54</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="C135" s="6" t="n">
-        <v>26.18</v>
+        <v>26.7</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>31.81</v>
@@ -10037,13 +10037,13 @@
         <v>13.04</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>0.0247</v>
+        <v>0.0194</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>0.0494</v>
+        <v>0.0387</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>0.0989</v>
+        <v>0.0775</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -10051,13 +10051,13 @@
         </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>13.98</v>
+        <v>14.15</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="M135" s="5" t="n">
         <v>0.29</v>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="D136" s="6" t="n">
         <v>6.75</v>
@@ -10104,13 +10104,13 @@
         <v>3.71</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>0.0374</v>
+        <v>0.0381</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0761</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>0.1496</v>
+        <v>0.1522</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="J136" s="5" t="n">
-        <v>11.94</v>
+        <v>11.92</v>
       </c>
       <c r="K136" s="5" t="n">
         <v>1</v>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="Q136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -10162,22 +10162,22 @@
         </is>
       </c>
       <c r="C137" s="6" t="n">
-        <v>0.145</v>
+        <v>0.135</v>
       </c>
       <c r="D137" s="6" t="n">
         <v>0.195</v>
       </c>
       <c r="E137" s="6" t="n">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.0259</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.0517</v>
+        <v>-0.0185</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.1034</v>
+        <v>-0.037</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
@@ -10185,13 +10185,13 @@
         </is>
       </c>
       <c r="J137" s="5" t="n">
-        <v>-11.34</v>
+        <v>-10.56</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="M137" s="5" t="n">
         <v>0.65</v>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>22.09</v>
+        <v>22.25</v>
       </c>
       <c r="D138" s="6" t="n">
         <v>29.24</v>
@@ -10238,13 +10238,13 @@
         <v>18.26</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>0.0149</v>
+        <v>0.0125</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>0.0298</v>
+        <v>0.0249</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>0.0596</v>
+        <v>0.0499</v>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="J138" s="5" t="n">
-        <v>19.9</v>
+        <v>20.05</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="M138" s="5" t="n">
         <v>0.68</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="Q138" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="Q139" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>46.15</v>
+        <v>46.57</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>46.79</v>
@@ -10380,13 +10380,13 @@
         <v>34.78</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>-0.0324</v>
+        <v>-0.0343</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0687</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>-0.1295</v>
+        <v>-0.1373</v>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="J140" s="5" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>6.18</v>
+        <v>6.23</v>
       </c>
       <c r="M140" s="5" t="n">
         <v>9.59</v>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="Q140" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:42</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>7.76</v>
+        <v>7.59</v>
       </c>
       <c r="D141" s="10" t="n">
         <v>8.24</v>
@@ -10447,13 +10447,13 @@
         <v>5.9</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>0.0244</v>
+        <v>0.0301</v>
       </c>
       <c r="G141" s="11" t="n">
-        <v>0.0488</v>
+        <v>0.0603</v>
       </c>
       <c r="H141" s="11" t="n">
-        <v>0.0975</v>
+        <v>0.1205</v>
       </c>
       <c r="I141" s="9" t="inlineStr">
         <is>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>21.56</v>
+        <v>21.08</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="L141" s="9" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="Q141" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>13.49</v>
+        <v>13.51</v>
       </c>
       <c r="D142" s="6" t="n">
         <v>20.2</v>
@@ -10516,13 +10516,13 @@
         <v>10.08</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>0.0061</v>
+        <v>0.0057</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.0115</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>0.0245</v>
+        <v>0.023</v>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="J142" s="5" t="n">
-        <v>15.69</v>
+        <v>15.71</v>
       </c>
       <c r="K142" s="5" t="n">
         <v>2.4</v>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="Q142" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>19.45</v>
+        <v>19.42</v>
       </c>
       <c r="D143" s="6" t="n">
         <v>21.92</v>
@@ -10583,13 +10583,13 @@
         <v>13.8</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>-0.0022</v>
+        <v>-0.0018</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>-0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H143" s="7" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0073</v>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
@@ -10597,10 +10597,10 @@
         </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>23.43</v>
+        <v>23.4</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L143" s="5" t="n">
         <v>1.37</v>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="Q144" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="C145" s="6" t="n">
-        <v>0.875</v>
+        <v>0.89</v>
       </c>
       <c r="D145" s="6" t="n">
         <v>1.19</v>
@@ -10725,13 +10725,13 @@
         <v>0.66</v>
       </c>
       <c r="F145" s="7" t="n">
-        <v>0.0334</v>
+        <v>0.0276</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>0.0668</v>
+        <v>0.0552</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>0.1336</v>
+        <v>0.1104</v>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
@@ -10739,13 +10739,13 @@
         </is>
       </c>
       <c r="J145" s="5" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="K145" s="5" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="M145" s="5" t="n">
         <v>0.67</v>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="D146" s="6" t="n">
         <v>15.62</v>
@@ -10792,13 +10792,13 @@
         <v>13.25</v>
       </c>
       <c r="F146" s="7" t="n">
-        <v>-0.0149</v>
+        <v>-0.0117</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>-0.0299</v>
+        <v>-0.0235</v>
       </c>
       <c r="H146" s="7" t="n">
-        <v>-0.0597</v>
+        <v>-0.0469</v>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="J146" s="5" t="n">
-        <v>99.33</v>
+        <v>98</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="Q146" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="C147" s="6" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="D147" s="6" t="n">
         <v>5.58</v>
@@ -10861,13 +10861,13 @@
         <v>4.705</v>
       </c>
       <c r="F147" s="7" t="n">
-        <v>0.0053</v>
+        <v>0.0094</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>0.0107</v>
+        <v>0.0189</v>
       </c>
       <c r="H147" s="7" t="n">
-        <v>0.0214</v>
+        <v>0.0377</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="J147" s="5" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>32.04</v>
+        <v>32.46</v>
       </c>
       <c r="D148" s="10" t="n">
         <v>41.44</v>
@@ -10930,13 +10930,13 @@
         <v>20.14</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>-0.0069</v>
+        <v>-0.01</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>-0.0137</v>
+        <v>-0.02</v>
       </c>
       <c r="H148" s="11" t="n">
-        <v>-0.0274</v>
+        <v>-0.04</v>
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
@@ -10944,13 +10944,13 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>74.51000000000001</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>24.46</v>
+        <v>24.78</v>
       </c>
       <c r="L148" s="9" t="n">
-        <v>16.62</v>
+        <v>16.83</v>
       </c>
       <c r="M148" s="9" t="n">
         <v>0.12</v>
@@ -10972,7 +10972,7 @@
       </c>
       <c r="Q148" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="C149" s="6" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="D149" s="6" t="n">
         <v>5.85</v>
@@ -10997,13 +10997,13 @@
         <v>3.47</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>0.0317</v>
+        <v>0.031</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>0.0635</v>
+        <v>0.0619</v>
       </c>
       <c r="H149" s="7" t="n">
-        <v>0.127</v>
+        <v>0.1238</v>
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="J149" s="5" t="n">
-        <v>119</v>
+        <v>119.33</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L149" s="5" t="n">
         <v>1.39</v>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>5.34</v>
+        <v>5.23</v>
       </c>
       <c r="D150" s="6" t="n">
         <v>8.205</v>
@@ -11064,13 +11064,13 @@
         <v>3.34</v>
       </c>
       <c r="F150" s="7" t="n">
-        <v>0.0047</v>
+        <v>0.0101</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>0.0094</v>
+        <v>0.0201</v>
       </c>
       <c r="H150" s="7" t="n">
-        <v>0.0189</v>
+        <v>0.0403</v>
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
@@ -11078,13 +11078,13 @@
         </is>
       </c>
       <c r="J150" s="5" t="n">
-        <v>15.85</v>
+        <v>15.52</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M150" s="5" t="n">
         <v>0.54</v>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="Q150" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="D152" s="10" t="n">
         <v>2.87</v>
@@ -11198,13 +11198,13 @@
         <v>1.695</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>0.0125</v>
+        <v>0.0185</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>0.025</v>
+        <v>0.037</v>
       </c>
       <c r="H152" s="11" t="n">
-        <v>0.05</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="I152" s="9" t="inlineStr">
         <is>
@@ -11212,10 +11212,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>11.49</v>
+        <v>11.24</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="L152" s="9" t="n">
         <v>0.15</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="Q152" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11256,22 +11256,22 @@
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>38.82</v>
+        <v>38.53</v>
       </c>
       <c r="D153" s="6" t="n">
         <v>43.32</v>
       </c>
       <c r="E153" s="6" t="n">
-        <v>33.32</v>
+        <v>33.53</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>-0.0326</v>
+        <v>-0.031</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0619</v>
       </c>
       <c r="H153" s="7" t="n">
-        <v>-0.1304</v>
+        <v>-0.1238</v>
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="J153" s="5" t="n">
-        <v>19.12</v>
+        <v>18.98</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="Q153" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>5.04</v>
@@ -11334,13 +11334,13 @@
         <v>2.17</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0735</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>0.1631</v>
+        <v>0.1471</v>
       </c>
       <c r="H154" s="11" t="n">
-        <v>0.3263</v>
+        <v>0.2942</v>
       </c>
       <c r="I154" s="9" t="inlineStr">
         <is>
@@ -11348,13 +11348,13 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="L154" s="9" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="M154" s="9" t="n">
         <v>0.44</v>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="Q154" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="C155" s="6" t="n">
-        <v>90.98999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="D155" s="6" t="n">
         <v>95.175</v>
@@ -11401,13 +11401,13 @@
         <v>70.8</v>
       </c>
       <c r="F155" s="7" t="n">
-        <v>-0.0389</v>
+        <v>-0.0395</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0791</v>
       </c>
       <c r="H155" s="7" t="n">
-        <v>-0.1555</v>
+        <v>-0.1581</v>
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="J155" s="5" t="n">
-        <v>33.7</v>
+        <v>33.81</v>
       </c>
       <c r="K155" s="5" t="n">
-        <v>13.15</v>
+        <v>13.19</v>
       </c>
       <c r="L155" s="5" t="n">
         <v>2.23</v>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="Q155" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="D156" s="6" t="n">
         <v>9.9</v>
@@ -11468,13 +11468,13 @@
         <v>5.94</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>0.0495</v>
+        <v>0.0491</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="H156" s="7" t="n">
-        <v>0.1981</v>
+        <v>0.1965</v>
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="J156" s="5" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="K156" s="5" t="n">
         <v>0.99</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Q156" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
         </is>
       </c>
       <c r="C157" s="6" t="n">
-        <v>10.87</v>
+        <v>11.01</v>
       </c>
       <c r="D157" s="6" t="n">
         <v>14.85</v>
@@ -11535,13 +11535,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="F157" s="7" t="n">
-        <v>0.036</v>
+        <v>0.0324</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H157" s="7" t="n">
-        <v>0.144</v>
+        <v>0.1294</v>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>16.47</v>
+        <v>16.68</v>
       </c>
       <c r="K157" s="5" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="Q157" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="Q158" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
         </is>
       </c>
       <c r="C159" s="6" t="n">
-        <v>32.95</v>
+        <v>31.78</v>
       </c>
       <c r="D159" s="6" t="n">
         <v>35.82</v>
@@ -11675,13 +11675,13 @@
         <v>21.96</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>-0.0009</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>-0.0019</v>
+        <v>0.017</v>
       </c>
       <c r="H159" s="7" t="n">
-        <v>-0.0038</v>
+        <v>0.034</v>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="J159" s="5" t="n">
-        <v>16.31</v>
+        <v>15.73</v>
       </c>
       <c r="K159" s="5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="M159" s="5" t="n">
         <v>0.34</v>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="Q159" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="D160" s="6" t="n">
         <v>2.82</v>
@@ -11742,13 +11742,13 @@
         <v>2.29</v>
       </c>
       <c r="F160" s="7" t="n">
-        <v>0.0164</v>
+        <v>0.0185</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>0.0327</v>
+        <v>0.037</v>
       </c>
       <c r="H160" s="7" t="n">
-        <v>0.0654</v>
+        <v>0.074</v>
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
@@ -11756,13 +11756,13 @@
         </is>
       </c>
       <c r="J160" s="5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K160" s="5" t="n">
-        <v>156.87</v>
+        <v>155.62</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>10.01</v>
+        <v>9.93</v>
       </c>
       <c r="M160" s="5" t="n">
         <v>0.49</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="Q160" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11800,7 +11800,7 @@
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>37.86</v>
+        <v>39.91</v>
       </c>
       <c r="D161" s="10" t="n">
         <v>117.79</v>
@@ -11809,13 +11809,13 @@
         <v>28.76</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>0.1809</v>
+        <v>0.1582</v>
       </c>
       <c r="G161" s="11" t="n">
-        <v>0.3618</v>
+        <v>0.3164</v>
       </c>
       <c r="H161" s="11" t="n">
-        <v>0.7237</v>
+        <v>0.6328</v>
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
@@ -11823,13 +11823,13 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>54.87</v>
+        <v>57.84</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>4.84</v>
+        <v>5.1</v>
       </c>
       <c r="L161" s="9" t="n">
-        <v>11.9</v>
+        <v>12.55</v>
       </c>
       <c r="M161" s="9" t="n">
         <v>1.33</v>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="Q161" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>73.8</v>
+        <v>75.14</v>
       </c>
       <c r="D162" s="10" t="n">
         <v>179.685</v>
@@ -11876,13 +11876,13 @@
         <v>61.45</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>0.1785</v>
+        <v>0.1707</v>
       </c>
       <c r="G162" s="11" t="n">
-        <v>0.3571</v>
+        <v>0.3414</v>
       </c>
       <c r="H162" s="11" t="n">
-        <v>0.7141</v>
+        <v>0.6827</v>
       </c>
       <c r="I162" s="9" t="inlineStr">
         <is>
@@ -11890,13 +11890,13 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>37.09</v>
+        <v>37.72</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="L162" s="9" t="n">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="M162" s="9" t="n">
         <v>0.39</v>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="Q162" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="D163" s="10" t="n">
         <v>4.93</v>
@@ -11943,13 +11943,13 @@
         <v>1.375</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>0.1271</v>
+        <v>0.0998</v>
       </c>
       <c r="G163" s="11" t="n">
-        <v>0.2541</v>
+        <v>0.1995</v>
       </c>
       <c r="H163" s="11" t="n">
-        <v>0.5083</v>
+        <v>0.3991</v>
       </c>
       <c r="I163" s="9" t="inlineStr">
         <is>
@@ -11957,13 +11957,13 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>33.62</v>
+        <v>36.25</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>5.14</v>
+        <v>5.54</v>
       </c>
       <c r="L163" s="9" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="M163" s="9" t="n">
         <v>3.82</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="Q163" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>0.255</v>
+        <v>0.265</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>0.39</v>
@@ -12133,13 +12133,13 @@
         <v>0.095</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.0343</v>
+        <v>0.0236</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0472</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.1373</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -12147,13 +12147,13 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-340.93</v>
+        <v>-354.3</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>1.39</v>
@@ -12170,12 +12170,12 @@
       </c>
       <c r="P2" s="8" t="inlineStr">
         <is>
-          <t>Core Lithium Ltd engages in the development of lithium and various metal deposits in Northern Territory and South Australia. Its flagship asset, the Finniss Lithium Operation, is hard-rock lithium project located on the Cox Peninsula. The company was incorporated in 2010 and is based in Perth, Australia.</t>
+          <t>Core Lithium Ltd engages in the development of lithium and various metal deposits in Northern Territory and South Australia. It primarily explores for gold, silver, uranium, lead, zinc, rare earth elements, and base metals. The company was incorporated in 2010 and is based in Perth, Australia.</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>2.65</v>
@@ -12275,13 +12275,13 @@
         <v>0.76</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.1152</v>
+        <v>0.1048</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.2304</v>
+        <v>0.2097</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4607</v>
+        <v>0.4194</v>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
@@ -12289,13 +12289,13 @@
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>8.99</v>
+        <v>9.26</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>8.09</v>
+        <v>8.33</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>1.28</v>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0.16</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>57.38</v>
+        <v>58.72</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.62</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0.27</v>
@@ -12411,13 +12411,13 @@
         <v>0.113</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2.0061</v>
+        <v>1.9195</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.0122</v>
+        <v>3.839</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8.0245</v>
+        <v>7.678</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -12425,13 +12425,13 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-11.45</v>
+        <v>-11.89</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>6.54</v>
+        <v>6.75</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>166.88</v>
+        <v>173.3</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>2.66</v>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0.46</v>
@@ -12478,13 +12478,13 @@
         <v>0.083</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.6627</v>
+        <v>0.6415</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1.3254</v>
+        <v>1.283</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2.6508</v>
+        <v>2.5659</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -12492,13 +12492,13 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-1.07</v>
+        <v>-1.09</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>10.61</v>
+        <v>10.86</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.12</v>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12536,22 +12536,22 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4.9</v>
+        <v>5.17</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>6.6</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.0564</v>
+        <v>0.0404</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.1129</v>
+        <v>0.0809</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.2258</v>
+        <v>0.1618</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>13.24</v>
+        <v>13.97</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>5.1</v>
+        <v>5.38</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>0.1</v>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.485</v>
+        <v>0.535</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0.892</v>
@@ -12612,13 +12612,13 @@
         <v>0.275</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.2655</v>
+        <v>0.2173</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.5309</v>
+        <v>0.4346</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.0619</v>
+        <v>0.8692</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -12631,10 +12631,10 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.66</v>
@@ -12656,7 +12656,7 @@
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>14.41</v>
+        <v>14.72</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>19.35</v>
@@ -12681,13 +12681,13 @@
         <v>8.26</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.1573</v>
+        <v>0.1488</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.3147</v>
+        <v>0.2975</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.6293</v>
+        <v>0.595</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -12695,13 +12695,13 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>206.57</v>
+        <v>211.01</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>8.1</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>6.07</v>
+        <v>6.2</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>1.12</v>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.175</v>
+        <v>0.185</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0.49</v>
@@ -12748,13 +12748,13 @@
         <v>0.155</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.0888</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.1776</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3551</v>
+        <v>0.2801</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -12762,13 +12762,13 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>3.47</v>
+        <v>3.67</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>2.54</v>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>9.59</v>
+        <v>9.99</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>15.1</v>
@@ -12815,13 +12815,13 @@
         <v>6.26</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.0617</v>
+        <v>0.0488</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.1234</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2467</v>
+        <v>0.1951</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -12829,13 +12829,13 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>39.71</v>
+        <v>41.65</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>17.34</v>
+        <v>18.06</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>0.19</v>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12873,22 +12873,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>19.9</v>
+        <v>20.65</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>21.75</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>10.96</v>
+        <v>11.03</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.0012</v>
+        <v>-0.008</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.0024</v>
+        <v>-0.0161</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.0047</v>
+        <v>-0.0321</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -12896,13 +12896,13 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>46.28</v>
+        <v>48.02</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>7.21</v>
+        <v>7.48</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>7.59</v>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.855</v>
+        <v>0.885</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>1.295</v>
@@ -12949,13 +12949,13 @@
         <v>0.665</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.1073</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.2147</v>
+        <v>0.1905</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.4294</v>
+        <v>0.3809</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -12963,13 +12963,13 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.11</v>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13007,7 +13007,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.915</v>
+        <v>0.895</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1.315</v>
@@ -13016,13 +13016,13 @@
         <v>0.755</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.0437</v>
+        <v>0.0503</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1006</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.1749</v>
+        <v>0.2011</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -13030,13 +13030,13 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-500</v>
+        <v>-489.07</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-18.3</v>
+        <v>-17.9</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>0.155</v>
@@ -13085,13 +13085,13 @@
         <v>0.033</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.9519</v>
+        <v>0.9074</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1.9038</v>
+        <v>1.8148</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>3.8077</v>
+        <v>3.6296</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -13099,10 +13099,10 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.15</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2.75</v>
@@ -13152,13 +13152,13 @@
         <v>1.05</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.2426</v>
+        <v>0.2077</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.4852</v>
+        <v>0.4154</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.8307</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -13166,13 +13166,13 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-32.41</v>
+        <v>-34.88</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>3.75</v>
+        <v>4.03</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-1162.61</v>
+        <v>-1251.28</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>1.45</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1.355</v>
+        <v>1.41</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>2.97</v>
@@ -13361,13 +13361,13 @@
         <v>1.215</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.1145</v>
+        <v>0.1003</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.229</v>
+        <v>0.2006</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.458</v>
+        <v>0.4011</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -13380,10 +13380,10 @@
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>-578.11</v>
+        <v>-601.58</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.51</v>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1.3</v>
+        <v>1.345</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2.2</v>
@@ -13430,13 +13430,13 @@
         <v>0.995</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0542</v>
+        <v>0.0441</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.1085</v>
+        <v>0.0881</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.217</v>
+        <v>0.1763</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -13444,13 +13444,13 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>7.96</v>
+        <v>8.23</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.92</v>
+        <v>5.09</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.09</v>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>7.52</v>
@@ -13710,13 +13710,13 @@
         <v>2.43</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.4115</v>
+        <v>0.4091</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.823</v>
+        <v>0.8182</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>1.646</v>
+        <v>1.6364</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -13724,13 +13724,13 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-21.24</v>
+        <v>-21.32</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0.93</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>178.44</v>
+        <v>179.09</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>4.76</v>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>0.28</v>
@@ -13866,13 +13866,13 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-2.26</v>
+        <v>-2.22</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -13971,7 +13971,7 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>18.97</v>
+        <v>19.53</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>22.22</v>
@@ -14138,13 +14138,13 @@
         <v>6.4</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.0529</v>
+        <v>0.0442</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.1058</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.2115</v>
+        <v>0.1768</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
@@ -14152,13 +14152,13 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>94.02</v>
+        <v>96.8</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>6.74</v>
+        <v>6.94</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>18.02</v>
+        <v>18.55</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>0.18</v>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>4.38</v>
+        <v>4.49</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>8.890000000000001</v>
@@ -14205,13 +14205,13 @@
         <v>2.11</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.286</v>
+        <v>0.2728</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>0.5719</v>
+        <v>0.5457</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>1.1438</v>
+        <v>1.0913</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
@@ -14219,13 +14219,13 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-45.15</v>
+        <v>-46.29</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>13.48</v>
+        <v>13.82</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>112.28</v>
+        <v>115.1</v>
       </c>
       <c r="M32" s="5" t="n">
         <v>0.48</v>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14338,22 +14338,22 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>5.16</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>2.605</v>
+        <v>2.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.1437</v>
+        <v>0.1179</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.2874</v>
+        <v>0.2358</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.5747</v>
+        <v>0.4716</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -14361,13 +14361,13 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>12.56</v>
+        <v>13.44</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>5.02</v>
+        <v>5.38</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>2.21</v>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:16</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14464,7 +14464,7 @@
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.25</v>
+        <v>0.258</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>0.325</v>
@@ -14489,13 +14489,13 @@
         <v>0.076</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.16</v>
+        <v>0.1481</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0.32</v>
+        <v>0.2961</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>0.64</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-12.5</v>
+        <v>-12.88</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>0.62</v>
@@ -14558,13 +14558,13 @@
         <v>0.17</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.1351</v>
+        <v>0.125</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.2703</v>
+        <v>0.25</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.5405</v>
+        <v>0.5</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -14572,15 +14572,13 @@
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-81.86</v>
+        <v>-84.06999999999999</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>1.28</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>771.13</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0.01</v>
@@ -14602,7 +14600,7 @@
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14616,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0.058</v>
@@ -14627,13 +14625,13 @@
         <v>0.014</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>2.25</v>
+        <v>2.4167</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>4.5</v>
+        <v>4.8333</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>9</v>
+        <v>9.666700000000001</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
@@ -14641,13 +14639,13 @@
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-4</v>
+        <v>-3.75</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>67.89</v>
+        <v>63.64</v>
       </c>
       <c r="M38" s="5" t="n">
         <v>0.09</v>
@@ -14669,7 +14667,7 @@
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14742,7 @@
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14758,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0.38</v>
@@ -14769,13 +14767,13 @@
         <v>0.095</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.4118</v>
+        <v>0.4318</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.8235</v>
+        <v>0.8636</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>1.6471</v>
+        <v>1.7273</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -14788,7 +14786,7 @@
         </is>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
@@ -14815,7 +14813,7 @@
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14831,13 +14829,13 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>0.215</v>
+        <v>0.225</v>
       </c>
       <c r="D41" s="6" t="n">
         <v>0.29</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="F41" s="7" t="n">
         <v/>
@@ -14859,10 +14857,10 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>9.35</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-8672.280000000001</v>
+        <v>-9075.639999999999</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
@@ -14886,7 +14884,7 @@
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14957,7 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15028,7 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15103,7 @@
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
@@ -15121,7 +15119,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>0.26</v>
@@ -15149,10 +15147,10 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>1044.91</v>
+        <v>1080.95</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.46</v>
@@ -15174,7 +15172,7 @@
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 23:43</t>
         </is>
       </c>
     </row>
